--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/KENTUCKY_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/KENTUCKY_2014.xlsx
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C201">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C209">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C468">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C522">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C539">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C750">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C860">
